--- a/reports/review/exp03_register_check_40.xlsx
+++ b/reports/review/exp03_register_check_40.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="instruções" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="itens" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instruções" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="itens" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -592,8 +592,16 @@
           <t>Hydrops fetalis</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
@@ -618,8 +626,16 @@
           <t>Hearing impairment</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
@@ -645,8 +661,16 @@
           <t>Muscle weakness</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -671,8 +695,16 @@
           <t>Hypertelorism / Hipertelorismo</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -699,8 +731,16 @@
           <t>Global developmental delay</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
@@ -726,8 +766,16 @@
           <t>Global developmental delay</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
@@ -752,8 +800,16 @@
           <t>Hemiparesis</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
@@ -779,8 +835,16 @@
           <t>Multiple lentigines</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -805,8 +869,16 @@
           <t>Entropion / Entrópio</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -831,8 +903,16 @@
           <t>Moderate intellectual disability</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -858,8 +938,16 @@
           <t>Flat face</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
@@ -884,8 +972,16 @@
           <t>Postaxial foot polydactyly</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -911,8 +1007,16 @@
           <t>Umbilical hernia</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -938,8 +1042,16 @@
           <t>Bilateral tonic-clonic seizure</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -965,8 +1077,16 @@
           <t>Pleural effusion</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -992,8 +1112,16 @@
           <t>Hypoplasia of the corpus callosum</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1019,8 +1147,16 @@
           <t>Hypertelorism / Hipertelorismo</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1047,8 +1183,16 @@
           <t>Anosmia / Anosmia</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1072,8 +1216,16 @@
           <t>Broad thumb</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1099,8 +1251,16 @@
           <t>Reduced cerebral white matter volume / Redução do volume da substância branca cerebral</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1125,8 +1285,16 @@
           <t>Focal-onset seizure / Convulsão de inicio focal</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1151,8 +1319,16 @@
           <t>Neurodevelopmental delay / Atraso no desenvolvimento neurológico</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1179,8 +1355,16 @@
           <t>Scoliosis</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1207,8 +1391,16 @@
           <t>Anemia</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1234,8 +1426,16 @@
           <t>Brisk reflexes</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1261,8 +1461,16 @@
           <t>Delayed ability to walk</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1289,8 +1497,16 @@
           <t>Taurodontia</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1315,8 +1531,16 @@
           <t>Hematochezia</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1342,8 +1566,16 @@
           <t>Lower limb pain / Dor na perna</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1368,8 +1600,16 @@
           <t>Reduced visual acuity / Acuidade visual reduzida</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1394,8 +1634,16 @@
           <t>Recurrent fever</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1422,8 +1670,16 @@
           <t>Optic disc coloboma / Coloboma do nervo óptico</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1448,8 +1704,16 @@
           <t>Delayed speech and language development</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1475,8 +1739,16 @@
           <t>Profound intellectual disability</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1502,8 +1774,16 @@
           <t>Hypotonia</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1530,8 +1810,16 @@
           <t>Global developmental delay</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1557,8 +1845,16 @@
           <t>Hypotonia</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1585,8 +1881,16 @@
           <t>Long philtrum / Filtro longo</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1613,8 +1917,16 @@
           <t>Short stature / Baixa estatura</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1640,8 +1952,16 @@
           <t>Bilateral sensorineural hearing impairment</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr"/>
     </row>
   </sheetData>
